--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_点検指摘への対応" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_事実確認の結果" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_受入ゲートの充足状況" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_残る課題と当方の見解" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,7 +1034,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>自己点検記録29件（重大11・中14・軽微4）を「対応済・対応中・資料待ち・判断待ち」に再分類すべき。</t>
+          <t>自己点検による指摘29件（重大11・中14・軽微4）を「対応済・対応中・資料待ち・判断待ち」に再分類すべき。</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -1043,7 +1044,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>当方の「第9期評価の自己点検記録」は08_対応の実施結果シートで対応状況を管理している。レビューの指摘は、この分類が委員会資料の作成に耐えるかを問うものである。</t>
+          <t>当方の「受託者の自己点検」は08_対応の実施結果シートで対応状況を管理している。レビューの指摘は、この分類が委員会資料の作成に耐えるかを問うものである。</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -2056,4 +2057,235 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>残る課題と、当方の見解</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>点検で挙がった提案のうち、そのままでは採れないもの及び補足を要するものについて当方の見解を述べる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>レビューの提案</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>当方の見解</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="76" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>委員会に出す表から「対応中」をなくす（P1-4）</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>そのままでは満たせない</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>第9期評価の指摘29件のうち、資料の受領を待つものが含まれる。これらを「対応中」から外すには資料が要る。資料待ちであることを隠すと、かえって評価の確からしさを誤って伝えることになる。</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>「資料待ち」と「対応中」を分けて表示する。資料待ちの件数と内容を明示する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>本文の要協議番号と別管理表のIDを完全一致させる（P2-4）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>本文へのID付与は採らない</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>計画本文は住民及び委員が読むものであり、内部管理用のIDを本文に置くと読みにくくなる。章節で特定できるため、決定事項一覧の側で対応させる方が実務に合う。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>03シートで章節別に対応させた。本文へのID付与の要否は発注者の決定による</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>調査分析95％は「分析成果物の作成率」であり「確定値の受入率」ではない（5章）</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>そのとおりである</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>当方の工程管理表は作成率で進捗を示していた。確定値の受入率で見ると、確定値表10件のうち確定は2件（20％）である。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>業務工程管理表に「作成率」と「確定値の受入率」の2つの欄を設ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>8月末を「未受領時の扱いも含めて評価方法を確定する締切」とする（7章）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>同意する</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>資料の受領を待って全体が止まることを避けられる。当方も暫定評価ルールを用意した。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>決定5として発注者の承認を求める</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>資料提供依頼の番号が2つの管理表で異なる</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>当方の管理上の不備である</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>業務工程管理表06シートでは「No.13」、必要事項の一覧では「No.1」として同じ資料（令和6〜8年度の施策・事業実績）を管理していた。レビューはNo.13で参照しており、外部から見ると同定できない。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>番号を業務工程管理表06シートに統一する。本改訂では未着手であり、次回の改訂で行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>全体進捗60％への更新（5章）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>妥当である</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>第9期評価65％（実績未受領のため75％から引下げ）、成果品45％（索引・版の是正を要する）等の引下げはいずれも根拠がある。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>業務工程管理表に反映する。本改訂では未着手であり、次回の改訂で行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>注1）⑤（資料提供依頼の番号の不統一）は、レビューの指摘には含まれていないが、レビューがNo.13と参照していることから当方が気づいたものである。同じ資料を2つの番号で管理しており、発注者に混乱を生じさせている。注2）⑤⑥は本改訂では未着手である。業務工程管理表と必要事項の一覧の改訂は次回にまとめて行う。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A12:E12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -1906,7 +1906,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>照会票・未回答時の扱い・確定値表を作成し、発出の準備を終えた。照会そのものは未発出である。確定値表10件のうち確定は2件（訪問介護員等181人、H12の20.4％）。</t>
+          <t>照会票・未回答時の扱い・確定値表を作成し、発出の準備を終えた。照会そのものは未発出である。確定値表10件のうち確定は2件（訪問介護員等181人、H12の代理指標20.4％）。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、協議用素案（令和8年8月時点）に残る［要協議］等90箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等88箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>本文に残る90箇所を、決定の単位で12件にまとめた。それぞれに選択肢・推奨案・影響・決定者・期限を付している。最高優先は決定1（人口推計の基礎）、決定2（認定率のシナリオ）、決定7（調査の集計方法）の3件である。この3件が決まらないと第6章が確定しない。</t>
+          <t>本文に残るプレースホルダを、決定の単位で12件にまとめた。それぞれに選択肢・推奨案・影響・決定者・期限を付している。最高優先は決定1（人口推計の基礎）、決定2（認定率のシナリオ）、決定7（調査の集計方法）の3件である。この3件が決まらないと第6章が確定しない。</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>本文の90箇所を12件の決定事項に集約し、選択肢・推奨案・影響・決定者・期限を付した（03・04シート）。本文のプレースホルダは運用方針により残している。</t>
+          <t>本文のプレースホルダを12件の決定事項に集約し、選択肢・推奨案・影響・決定者・期限を付した（03・04シート）。本文のプレースホルダは運用方針により残している。</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等88箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等128箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等128箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等138箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_レビュー対応記録.xlsx
+++ b/output/第10期計画_レビュー対応記録.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等138箇所を委員会決定事項として12件に集約した。</t>
+          <t>受領したレビューの指摘13件について、事実関係を確認したうえで対応の可否と内容を示す。あわせて指摘P1-3及び受入ゲートE5に対応し、計画素案に残る［要協議］等140箇所を委員会決定事項として12件に集約した。</t>
         </is>
       </c>
     </row>
@@ -1598,17 +1598,17 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>667段落114表</t>
+          <t>806段落130表36図（実物）</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>改訂により増えた</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>python-docxにより数えた。図は34点で変わらない</t>
+          <t>令和8年9月11日の点検で、管理表の記載が実物とずれていることが分かった。以後は実物から数える（repo_paths.draft_label）。本欄の667段落114表34図は本改訂の時点の値である</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>解消</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>改訂前の値が残っていた。本改訂で667段落114表に更新した</t>
+          <t>改訂前の値が残っていた。本改訂で667段落114表に更新し、令和8年9月11日に固定値をやめて実物から数える形に改めた</t>
         </is>
       </c>
     </row>
